--- a/financeiro/2026-07/precos-custos.xlsx
+++ b/financeiro/2026-07/precos-custos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C248"/>
+  <dimension ref="A1:C256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4135,6 +4135,126 @@
         <v>226</v>
       </c>
     </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>ESP. C. GEISSE BLANC DE BLANC C/ 6GFAS 750 ML</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>123.02</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>ORNELLAIA SRL POGGIO ALLE GAZZE DELL'ORNELLAIA TOSCANA 2023</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>1327.7778</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>ORNELLAIA SRL POGGIO ALLE GAZZE DELL'ORNELLAIA TOSCANA 2023</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>599.0741</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>MASSOLINO BAROLO PARUSSI TTO 750 ML</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>1149.7963</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>MASSOLINO BARBARESCO TTO 750 ML</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>517.1667</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>MASSOLINO DOLCETTO D ALBA TT 750 ML</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>167.0185</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>MASSOLINO MOSCATO D ASTI BCO 375 ML</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>90.2222</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>MASSOLINO BARBERA D ALBA TTO 750 ML</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>205.6852</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
